--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -544,18 +544,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -616,7 +634,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -643,12 +661,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,6 +683,11 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -671,27 +695,49 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="D2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,13 +751,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -735,7 +781,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -745,8 +791,8 @@
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
-    <col width="21" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -757,7 +803,7 @@
     <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1079,10 +1125,8 @@
           <t>Aakriti Gautam</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9818672702</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9818672702</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1141,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9818672702</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9818672702</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1159,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.700424</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.700424</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1172,47 +1212,43 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L54-8</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.35173</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.35173</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>14h 12m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : Secondary router   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>14h 12m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : Secondary router   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -1221,6 +1257,206 @@
       <c r="AX2" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:03 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340016</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Madan raj nath</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Madan raj nath</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9748853357</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:53:52 PM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9851124544</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:53:52 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:03:46 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur	tempo park, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -546,7 +546,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -562,20 +562,38 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="B5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -590,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -634,7 +652,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -646,7 +664,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -661,13 +702,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -678,15 +720,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -702,16 +749,19 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -720,24 +770,49 @@
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -751,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -762,25 +837,25 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -788,10 +863,10 @@
     <col width="27" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1327,10 +1402,8 @@
           <t>Madan raj nath</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9748853357</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9748853357</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1345,10 +1418,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9851124544</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9851124544</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1412,10 +1483,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1426,37 +1495,453 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>19h 9m</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>19h 9m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:27 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340296</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Bidur GHimire</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Bidur GHimire</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9844770214</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:27:15 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>LTP9844770214</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:43:49 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:27:15 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Suryanagar, Ward No.4, Imadol, Lalitpur, Nepal. - Housing society M83X+G49 Mahalaxmi 44700, Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>9844770214@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>16h 43m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:21 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>one light blinking</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339492</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:50:08 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:07:35 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:21:14 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Dhimelwah Kumari Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>grg42589@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 13m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -580,20 +580,38 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -652,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -675,10 +693,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -687,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -702,14 +720,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,6 +754,11 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -754,8 +778,11 @@
       <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>2</v>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -773,8 +800,11 @@
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -792,7 +822,10 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -812,7 +845,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -839,10 +875,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -860,7 +896,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1596,10 +1632,8 @@
           <t>Bidur GHimire</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9844770214</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9844770214</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1689,10 +1723,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1703,7 +1735,7 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1804,10 +1836,8 @@
           <t>Shanta Mukhiya</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9849090123</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9849090123</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1879,10 +1909,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH5" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI5" s="3" t="inlineStr"/>
       <c r="AJ5" s="3" t="inlineStr"/>
@@ -1897,10 +1925,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1911,29 +1937,29 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 13m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>23h 31m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>1d 13m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -1942,6 +1968,638 @@
       <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:47 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340024</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9813393411</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:14:36 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9849998104</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:27 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:47:21 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Shree Jana Kalyan High School - Government school M6PQ+332 Chandragiri , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>umeshlama44@email.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>CDB442</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>19h 49m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:46 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340024</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Lal Muktan</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9813393411</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:14:36 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9849998104</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:27 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:47:21 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Shree Jana Kalyan High School - Government school M6PQ+332 Chandragiri , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>umeshlama44@email.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB442</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>19h 49m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:44 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338679</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Nischit Shrestha</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Nischit Shrestha</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9840184282</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:21:13 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9840184282</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:21:13 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:44:22 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.702095</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>P72Q+VQQ, Tahachal Marg, Kathmandu 44600 Near by Muna Dairy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>shresthanischit18@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>08:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>CDB218</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.289872</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -776,13 +776,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -810,7 +810,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -830,25 +830,47 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="D6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>6</v>
+      <c r="F6" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -862,11 +884,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -2038,10 +2060,8 @@
           <t>Bhim Lal Muktan</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9813393411</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9813393411</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2131,10 +2151,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -2145,7 +2163,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2246,10 +2264,8 @@
           <t>Bhim Lal Muktan</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9813393411</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9813393411</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2339,10 +2355,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -2353,7 +2367,7 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2454,10 +2468,8 @@
           <t>Nischit Shrestha</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9840184282</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9840184282</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2492,10 +2504,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.702095</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.702095</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2551,47 +2561,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>CDB218</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.289872</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.289872</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 23m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 23m</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>1d 22h 23m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -2600,6 +2606,522 @@
       <c r="AX8" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340472</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9849450663</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9842424578</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:00:08 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>3D Art World - Interactive Museum - Art center M82R+PW2 Mahalaxmi 44700, , ,</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>kcsabin544@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>15h 40m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>15h 40m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:54 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340472</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9849450663</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9842424578</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:00:08 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>3D Art World - Interactive Museum - Art center M82R+PW2 Mahalaxmi 44700, , ,</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>kcsabin544@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>15h 40m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>15h 40m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 9:52 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -546,72 +546,90 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>40.0%</t>
+      <c r="B7" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -682,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -693,10 +711,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -705,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -720,15 +738,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -744,20 +763,25 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -773,16 +797,19 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="E2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>4</v>
+      <c r="G2" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -801,9 +828,12 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -817,15 +847,18 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -839,15 +872,18 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -861,16 +897,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="E6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>8</v>
+      <c r="G6" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -884,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -897,10 +936,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -918,7 +957,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -2676,10 +2715,8 @@
           <t>Sabin K.C</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9849450663</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9849450663</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2765,10 +2802,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2779,7 +2814,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2880,10 +2915,8 @@
           <t>Sabin K.C</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9849450663</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9849450663</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2969,10 +3002,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2983,7 +3014,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3125,6 +3156,422 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:16 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339713</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Yashaswee Shrestha</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Yashaswee Shrestha</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9823050565</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:16:09 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9823050565</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:24:26 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:16:09 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.66315</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Near Covenant Academy, Kusunti, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>yashasweeshrestha77@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>00:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.3103</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>22h 51m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:05 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340263</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:05:05 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>27. 658629 85.314654, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -840,7 +840,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -850,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -888,28 +888,53 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="E7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>10</v>
+      <c r="G7" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX13"/>
+  <dimension ref="A1:AX14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -934,14 +959,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -951,7 +976,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -3223,10 +3248,8 @@
           <t>Yashaswee Shrestha</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9823050565</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9823050565</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3261,10 +3284,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.66315</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.66315</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3320,25 +3341,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.3103</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.3103</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3439,10 +3456,8 @@
           <t>Bhagawati bhandari</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9855024115</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9855024115</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3524,10 +3539,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -3538,35 +3551,251 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>17h 40m</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>17h 40m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>internet not working as it has power issue</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340869</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Arya Singh</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Arya Singh</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9860556583</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:30:50 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9860556583</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 07:42:47 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:30:50 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.67125</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Unique Driving School - Drivers license training school Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>ajayarya750@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>00:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB424</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.347486</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -806,10 +806,10 @@
         <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -931,10 +931,10 @@
         <v>5</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -948,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX14"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3652,10 +3652,8 @@
           <t>Ajay Arya Singh</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9860556583</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9860556583</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3690,10 +3688,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.67125</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.67125</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3749,55 +3745,691 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB424</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.347486</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.347486</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
           <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS14" s="3" t="inlineStr">
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:35 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>one light blinking</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339492</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:37:14 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:07:35 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:37:14 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Dhimelwah Kumari Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>grg42589@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>2h 48m</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV14" s="3" t="inlineStr">
-        <is>
-          <t>Case : internet not working as it has power issue  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW14" s="3" t="inlineStr">
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 29m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX14" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:34 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338831</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9849632777</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:57:33 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9849632777</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:34:14 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.70417</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Telecom,Chhauni, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>ravig4279@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>07:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB115</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.2889</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>15h 36m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 19m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:33 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338831</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Anuj Gautam</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9849632777</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:57:33 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9849632777</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:14:24 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:34:14 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.70417</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Telecom,Chhauni, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>ravig4279@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>07:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB115</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.2889</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>15h 36m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 19m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -582,54 +582,72 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -700,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -723,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -948,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -994,7 +1012,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3860,10 +3878,8 @@
           <t>Shanta Mukhiya</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9849090123</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9849090123</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3935,10 +3951,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH15" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH15" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="inlineStr"/>
       <c r="AJ15" s="3" t="inlineStr"/>
@@ -3953,10 +3967,8 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -3967,7 +3979,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -4068,10 +4080,8 @@
           <t>Anuj Gautam</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9849632777</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9849632777</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4106,10 +4116,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.70417</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.70417</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4165,25 +4173,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>CDB115</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.2889</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.2889</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4284,10 +4288,8 @@
           <t>Anuj Gautam</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9849632777</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9849632777</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4322,10 +4324,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.70417</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.70417</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4381,47 +4381,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>CDB115</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.2889</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.2889</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>15h 36m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 19m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>15h 36m</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>1d 21h 19m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 Router   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -4430,6 +4426,114 @@
       <c r="AX17" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:49 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr"/>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="3" t="inlineStr"/>
+      <c r="X18" s="3" t="inlineStr"/>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr"/>
+      <c r="AA18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr"/>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr"/>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr"/>
+      <c r="AM18" s="3" t="inlineStr"/>
+      <c r="AN18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4537,6 +4537,222 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:12 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr"/>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="AA19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:10 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr"/>
+      <c r="V20" s="3" t="inlineStr"/>
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="inlineStr"/>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -883,17 +883,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -918,41 +918,91 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>12</v>
+      <c r="F9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -966,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AX23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1012,7 +1062,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4753,6 +4803,630 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:05 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340263</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:05:47 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>27. 658629 85.314654, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:07 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Net TV</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339347</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:07:35 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:03 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:07:35 AM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.70089</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>kwahiti marga near suzuki showroom and near siddhi ganesh motorcycle workshop teku, Bagmati, Central</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>vgajurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>01:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.30298</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 13h 24m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:08 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339241</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9746625579</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:30:16 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>KLK9746625579</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:30:28 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:08:50 AM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>27.72239895777987,85.29581583282115, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>naomidon07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>01:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB165</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h 38m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 38m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -756,16 +756,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -791,15 +792,20 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -812,7 +818,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
@@ -821,13 +827,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>7</v>
+      <c r="H2" s="6" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -849,16 +858,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -876,8 +888,11 @@
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -901,14 +916,17 @@
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -926,7 +944,10 @@
       <c r="F6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -951,7 +972,10 @@
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -976,7 +1000,10 @@
       <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -987,7 +1014,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1</v>
@@ -996,13 +1023,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1016,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX23"/>
+  <dimension ref="A1:AX31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1029,10 +1059,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1043,7 +1073,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -1056,11 +1086,11 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
@@ -4870,10 +4900,8 @@
           <t>Bhagawati bhandari</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9855024115</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9855024115</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4955,10 +4983,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4969,7 +4995,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -5070,10 +5096,8 @@
           <t>Bikram Gajurel</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9803749646</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9803749646</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5108,10 +5132,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.70089</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.70089</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5167,25 +5189,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.30298</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.30298000000001</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5276,20 +5294,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M23" s="3" t="inlineStr"/>
       <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Prabin Chaudhary</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9746625579</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9746625579</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5379,10 +5391,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -5393,35 +5403,1715 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h 38m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 38m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
           <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>1d 14h 38m</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>1d 15h 38m</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:53 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341085</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Singh Thakuri</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Singh Thakuri</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9843276614</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:53:03 AM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9843276614</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:39:19 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:53:03 AM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.67176</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Near Unique Fuel Center, Balkumari, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>ashishthakuri555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>01:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB016</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.33838</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1h 13m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57 AM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340125</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Kaji bahadur gurung</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Kaji bahadur gurung</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9841025017</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:13 AM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841025017</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:09:06 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:13 AM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh than, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>ngawanggurung233@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>01:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>20h 48m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:35 AM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340251</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Goma sangroula</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Goma sangroula</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9763578233</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:35:52 AM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9864337003</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:20:21 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:35:52 AM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.7267498</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Sat-tale	Sat-tale, kapan	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Nepali</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L13-4</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.3518059</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>19h 15m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341146</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9708030031</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:00:12 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>CHB9708030031</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:17:20 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:00:12 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Bhotebahal Futsal - Futsal court M8W6+G76 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>9708030031@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>CDB015</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>42m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57 AM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339909</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Sanju Trade and Suppliers</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Sanju Trade and Suppliers</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9849015652</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:42 AM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>CHB9849015652</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:58:02 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:57:42 AM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Newa Petrol Pump - Gas station P873+P8G Pushpalal Path Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>9849015652@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>01:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>22h 59m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:56 AM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340731</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>prajol Jha</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>prajol Jha</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9843507007</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:56:55 AM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9843507007</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:56:49 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:56:55 AM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.702937</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Near by Kathmandu Metropolitan City Office Ward No. 20, P833+4C2, Lati Bunga Galli, Kathmandu 44600,</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>prazol93@gmail.Com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>01:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.303953</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:59 AM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340727</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Kamala gharti magar</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Kamala gharti magar</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9860205079</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:53:45 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9860205079</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:53:45 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:59:30 AM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Height Micro Station - Bus station Kathmandu 44600 - Kathmandu Metropolitan, Kathmandu, Bagma</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>CDB497</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>15h 5m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>15h 5m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:55 AM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340847</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Bogati</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Bogati</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9860767850</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 07:01:52 AM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9860767805</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 07:01:52 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:55:33 AM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.74837</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Summer Angels Montessori Pre-school - Kindergarten P7XR+57W Trishuli Hwy Tarakeshwar 44600, Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>01:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L60-4</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.290551</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>4h 53m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>4h 53m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW23" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX23" s="3" t="inlineStr">
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -833,10 +833,10 @@
         <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1029,10 +1029,10 @@
         <v>6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX31"/>
+  <dimension ref="A1:AX32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5504,10 +5504,8 @@
           <t>Prakash Singh Thakuri</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9843276614</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9843276614</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5542,10 +5540,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.67176</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.67176</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5583,10 +5579,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH24" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH24" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
@@ -5605,25 +5599,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB016</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.33838</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.33838</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5724,10 +5714,8 @@
           <t>Kaji bahadur gurung</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9841025017</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9841025017</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5817,10 +5805,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -5831,7 +5817,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection     has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5932,10 +5918,8 @@
           <t>Goma sangroula</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9763578233</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9763578233</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5970,10 +5954,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.7267498</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.7267498</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -6021,25 +6003,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L13-4</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.3518059</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.3518059</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -6140,10 +6118,8 @@
           <t>Sirjana Gurung</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9708030031</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9708030031</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6229,10 +6205,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -6243,7 +6217,7 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6344,10 +6318,8 @@
           <t>Sanju Trade and Suppliers</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9849015652</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9849015652</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6419,10 +6391,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH28" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH28" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
@@ -6441,10 +6411,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -6455,7 +6423,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6556,10 +6524,8 @@
           <t>prajol Jha</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9843507007</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9843507007</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6594,10 +6560,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.702937</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.702937</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6653,25 +6617,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>4,15</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.303953</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.30395300000001</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6772,10 +6732,8 @@
           <t>Kamala gharti magar</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9860205079</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9860205079</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6857,10 +6815,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6871,7 +6827,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6972,10 +6928,8 @@
           <t>Sanjay Bogati</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9860767850</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9860767850</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -7010,10 +6964,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.74837</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.74837</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -7065,53 +7017,265 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>L60-4</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.290551</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.29055099999999</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>4h 53m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>4h 53m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>4h 53m</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>4h 53m</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV31" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:02 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340880</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Spandan Bhatta</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9823009955</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:02:21 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9823009955</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 08:02:00 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:02:21 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.73269</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Kharibot, Siddhartha tol-16, Next to Simon Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>bhattaspandan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>02:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Maharjan</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.29153</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -1092,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7132,10 +7132,8 @@
           <t>Spandan Bhatta</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9823009955</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9823009955</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7170,10 +7168,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.73269</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.73269</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -7229,25 +7225,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>CDB348</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.29153</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.29152999999999</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1017,7 +1017,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>2</v>
@@ -1032,7 +1032,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AX33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1059,10 +1059,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1092,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7273,6 +7273,214 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:31 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340254</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Synapse Technologies Pvt.Ltd</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Synapse Technologies Pvt.Ltd</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9862407759</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:31:30 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>LTP9862407759</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:21:48 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:31:30 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Thulo: All-in-One Business Software Thulo: All-in-One Business Software - Software company Jwagal Ma</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>9862407759@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>02:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>20h 9m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -827,16 +827,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -864,7 +864,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>2</v>
@@ -1023,16 +1023,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX33"/>
+  <dimension ref="A1:AX37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1076,7 +1076,7 @@
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -1086,7 +1086,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1095,7 +1095,7 @@
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="36" customWidth="1" min="47" max="47"/>
+    <col width="45" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -7340,10 +7340,8 @@
           <t>Synapse Technologies Pvt.Ltd</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9862407759</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9862407759</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7433,10 +7431,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -7447,37 +7443,781 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>20h 9m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:48 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341153</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Wang Chu Sherpa</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Wang Chu Sherpa</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9745727416</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:48:41 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9745727416</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:24:31 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:48:41 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Lords Eco Inn, Kathmandu - Hotel Tushal-Mahankal Rd Kathmandu 44602 , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>wangchusherpatkd@gamail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>01:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>L44-1</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>20h 9m</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1h 24m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW33" s="3" t="inlineStr">
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX33" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr"/>
+      <c r="W35" s="3" t="inlineStr"/>
+      <c r="X35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="AA35" s="3" t="inlineStr"/>
+      <c r="AB35" s="3" t="inlineStr"/>
+      <c r="AC35" s="3" t="inlineStr"/>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr"/>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr"/>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr"/>
+      <c r="AM35" s="3" t="inlineStr"/>
+      <c r="AN35" s="3" t="inlineStr"/>
+      <c r="AO35" s="3" t="inlineStr"/>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>one light blinking</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341187</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Aafrin Timalsina</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Aafrin Timalsina</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9840184570</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49:09 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9840184570</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:46:49 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:52:41 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.707155</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Balkumari Temple P846+QJM, Siddhidas Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>aafrinbanu104@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>CDB504</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.310937</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1h 5m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341022</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjib sahi</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjib sahi</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9849198629</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:04:24 AM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9849198629</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:04:24 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49:29 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.701051</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Bafal near narayani petrol pump, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr"/>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>02:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.283079</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1017,7 +1017,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>2</v>
@@ -1032,7 +1032,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX37"/>
+  <dimension ref="A1:AX38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7544,10 +7544,8 @@
           <t>Wang Chu Sherpa</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9745727416</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9745727416</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7619,10 +7617,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH34" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH34" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
@@ -7641,10 +7637,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -7655,7 +7649,7 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -7864,10 +7858,8 @@
           <t>Aafrin Timalsina</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9840184570</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9840184570</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7902,10 +7894,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.707155</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.707155</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7957,25 +7947,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>CDB504</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.310937</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.310937</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -8076,10 +8062,8 @@
           <t>Sanjib sahi</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9849198629</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9849198629</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8114,10 +8098,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.701051</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.701051</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -8169,47 +8151,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.283079</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.283079</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>2h 45m</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>2h 45m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router    has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -8218,6 +8196,214 @@
       <c r="AX37" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 1:13 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340950</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Nepal</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Nepal</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9709639855</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:13:50 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>LTP9709639855</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:18:01 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:13:50 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Citizen Bank International Limited - Bank M8QP+355 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>03:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>3h 55m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -1092,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -8266,10 +8266,8 @@
           <t>Bijay Nepal</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9709639855</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9709639855</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8359,10 +8357,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
@@ -8373,7 +8369,7 @@
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>28.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX38"/>
+  <dimension ref="A1:AX40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8403,6 +8403,222 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr"/>
+      <c r="X39" s="3" t="inlineStr"/>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr"/>
+      <c r="AA39" s="3" t="inlineStr"/>
+      <c r="AB39" s="3" t="inlineStr"/>
+      <c r="AC39" s="3" t="inlineStr"/>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr"/>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr"/>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr"/>
+      <c r="AM39" s="3" t="inlineStr"/>
+      <c r="AN39" s="3" t="inlineStr"/>
+      <c r="AO39" s="3" t="inlineStr"/>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="inlineStr"/>
+      <c r="X40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="AA40" s="3" t="inlineStr"/>
+      <c r="AB40" s="3" t="inlineStr"/>
+      <c r="AC40" s="3" t="inlineStr"/>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr"/>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr"/>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr"/>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr"/>
+      <c r="AM40" s="3" t="inlineStr"/>
+      <c r="AN40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>31.7%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1020,7 +1020,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>3</v>
@@ -1032,7 +1032,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX40"/>
+  <dimension ref="A1:AX42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1092,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -8619,6 +8619,426 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:30 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Net TV</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339347</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Reopen</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:30:09 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:03 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:30:08 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.70089</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>kwahiti marga near suzuki showroom and near siddhi ganesh motorcycle workshop teku, Bagmati, Central</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>vgajurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr"/>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.30298</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>Negative Time</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 47m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (Reopen)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:29 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb box issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>stb box issue</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340536</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Rupesh Lamichhane</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Rupesh Lamichhane</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9841789993</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:13:47 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9841789993</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:54:23 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:29:19 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Pepsicola, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>rupeshlamichhane@ymail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L9-2</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb box issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>18h 15m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>19h 34m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb box issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -1092,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -8686,10 +8686,8 @@
           <t>Bikram Gajurel</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9803749646</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9803749646</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8724,10 +8722,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.70089</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.70089</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8779,25 +8775,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.30298</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.30298000000001</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : Net TV  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8898,10 +8890,8 @@
           <t>Rupesh Lamichhane</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9841789993</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9841789993</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8973,10 +8963,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH42" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI42" s="3" t="inlineStr"/>
       <c r="AJ42" s="3" t="inlineStr"/>
@@ -8991,10 +8979,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
@@ -9005,7 +8991,7 @@
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : stb box issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>14</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -836,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -926,7 +926,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -964,13 +964,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -982,17 +982,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -1008,31 +1008,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>29</v>
+      <c r="H10" s="4" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX42"/>
+  <dimension ref="A1:AX45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1092,7 +1120,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -9025,6 +9053,650 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:58 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341380</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9851220331</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:06:54 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9841863259</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:06:54 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:58:50 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.6907</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Chakrabarti Habi Education Academy College of Law,Bijulibazar, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr"/>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.32893</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>51m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>51m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:56 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Requesting to Downgrade wifi6 to wifi5</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332008</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Lokendra Shrestha</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Lokendra Shrestha</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9843414687</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:55:44 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9843414687</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 08:36:55 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:56:21 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.6749</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur-4,Dhobighat , At ASK LIVE FISH HOUSE, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>Lokebabi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr"/>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.30289</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>8d 6h 19m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 2:55 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Requesting to Downgrade wifi6 to wifi5</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332008</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Lokendra Shrestha</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Lokendra Shrestha</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9843414687</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:55:44 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9843414687</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 08:36:55 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:56:21 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.6749</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur-4,Dhobighat , At ASK LIVE FISH HOUSE, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>Lokebabi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr"/>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.30289</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>8d 6h 19m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>56.5%</t>
         </is>
       </c>
     </row>
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
@@ -836,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>3</v>
@@ -1060,7 +1060,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1074,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX45"/>
+  <dimension ref="A1:AX47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9120,10 +9120,8 @@
           <t>Aama Milan Kendra</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9851220331</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9851220331</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9158,10 +9156,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.6907</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.6907</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -9213,25 +9209,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L48-6</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.32893</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.32893</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -9332,10 +9324,8 @@
           <t>Lokendra Shrestha</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9843414687</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9843414687</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9370,10 +9360,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.6749</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.6749</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -9429,25 +9417,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.30289</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.30289</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9548,10 +9532,8 @@
           <t>Lokendra Shrestha</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9843414687</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9843414687</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9586,10 +9568,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.6749</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.6749</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9645,55 +9625,471 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.30289</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.30289</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>8d 6h 19m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
           <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:04 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341071</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Som Bahadur blon</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Som Bahadur blon</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9761898728</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:04:23 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9769369104</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:31:23 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:04:23 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur	Sanepa	Ram mandir, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr"/>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>04:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>8d 6h 19m</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>Case : Requesting to Downgrade wifi6 to wifi5  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW45" s="3" t="inlineStr">
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>4h 33m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX45" s="3" t="inlineStr">
+      <c r="AX46" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:05 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340686</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Shrestha</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Shrestha</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9803649633</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:05:45 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9824695909</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:23:20 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:05:45 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.676096</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Balkumari Temple,M9GP+944, ??????? ???? 44600,27.67699,85.38587, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>shtprasun@gmai.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>05:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>L62-1</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.385605</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>18h 42m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -1120,7 +1120,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -9740,10 +9740,8 @@
           <t>Som Bahadur blon</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9761898728</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9761898728</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9829,10 +9827,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
@@ -9843,7 +9839,7 @@
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -9944,10 +9940,8 @@
           <t>Rabi Shrestha</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9803649633</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9803649633</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9982,10 +9976,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.676096</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.676096</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -10041,25 +10033,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>L62-1</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.385605</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.385605</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -706,42 +706,65 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>61.5%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>56.5%</t>
+      <c r="B4" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>60.7%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -756,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -818,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -827,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>5</v>
@@ -836,7 +859,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -870,20 +893,20 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -892,32 +915,32 @@
         <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>2</v>
@@ -926,7 +949,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -936,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -954,7 +977,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -964,13 +987,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -1010,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1036,31 +1059,59 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>33</v>
+      <c r="H11" s="4" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1074,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX47"/>
+  <dimension ref="A1:AX53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1120,7 +1171,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -10081,6 +10132,1286 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340040</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Gita Raut</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Gita Raut</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9841292477</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:09 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9841292477</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:07:03 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:09 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.680562</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur near by Pipeline Road, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>9841292477@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>05:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>L54-8</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.441294</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 40m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:40 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>WIF 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340963</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Sujata Magar</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Sujata Magar</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9703759847</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:39:59 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9703759847</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 09:28:06 AM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:39:59 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.689029</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur 44600,Near Nightingale School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>heavant.619@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>05:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>CDB158</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.312733</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>6h 11m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:38 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341388</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Justice law chambers</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Justice law chambers</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9851046651</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:14:37 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9851046651</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:14:37 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:38:07 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.69272</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Opp to NMB Bank Limited NMB Bhawan, Akhtiyaar Marga, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>premagiri45@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.3266</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>1h 23m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1h 23m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:35 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341283</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Subedi</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Subedi</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9861587572</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:35:13 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9861587572</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 12:49:38 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:35:13 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>thali	Hariyali height, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr"/>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>02:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Shrestha</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L60-8</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>ipyv issue</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340284</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9761786202</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:57:42 AM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9869125880</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:35:54 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:16 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.69433</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri  Near By  New Diamond Academy School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>desirajan123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>05:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.26821</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>4h 49m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 3:46 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>ipyv issue</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340284</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Madhu Acharya</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9761786202</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10:57:42 AM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9869125880</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:35:54 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:47:16 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.69433</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri  Near By  New Diamond Academy School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>desirajan123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>05:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.26821</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>4h 49m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -1171,7 +1171,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -10199,10 +10199,8 @@
           <t>Gita Raut</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9841292477</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9841292477</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10237,10 +10235,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.680562</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.680562</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -10296,25 +10292,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>L54-8</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.441294</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.441294</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
@@ -10415,10 +10407,8 @@
           <t>Sujata Magar</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9703759847</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9703759847</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10453,10 +10443,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.689029</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.689029</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -10512,25 +10500,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>CDB158</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.312733</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.31273299999999</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : WIF 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -10631,10 +10615,8 @@
           <t>Justice law chambers</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9851046651</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9851046651</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10669,10 +10651,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.69272</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.69272</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -10724,25 +10704,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.3266</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.3266</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -10843,10 +10819,8 @@
           <t>Manoj Subedi</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9861587572</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9861587572</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10932,10 +10906,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -10946,7 +10918,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -11047,10 +11019,8 @@
           <t>Madhu Acharya</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9761786202</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9761786202</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -11085,10 +11055,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.69433</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.69433</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -11144,25 +11112,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.26821</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.26821</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -11263,10 +11227,8 @@
           <t>Madhu Acharya</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9761786202</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9761786202</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -11301,10 +11263,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.69433</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.69433</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -11360,25 +11320,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.26821</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.26821</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : ipyv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>17</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
     </row>
@@ -853,13 +853,13 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>4</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1125,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX53"/>
+  <dimension ref="A1:AX55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1171,7 +1171,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -11368,6 +11368,422 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:15 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340263</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:15:03 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>27. 658629 85.314654, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr"/>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr"/>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>23h 50m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>23h 50m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:07 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341353</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Neema Tamang</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Neema Tamang</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9824916928</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:07:50 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9803622158</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:42:30 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:07:50 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.67986</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu, Koteshower Haryali Banquet, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>neematamang02@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>02:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.33749</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>2h 25m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>28</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.9%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.8%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -859,23 +859,23 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -893,17 +893,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -1061,17 +1061,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -1087,31 +1087,59 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B12" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>39</v>
+      <c r="H12" s="4" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1125,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX55"/>
+  <dimension ref="A1:AX57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1138,10 +1166,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -11435,10 +11463,8 @@
           <t>Bhagawati bhandari</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9855024115</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9855024115</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -11520,10 +11546,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -11534,7 +11558,7 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -11635,10 +11659,8 @@
           <t>Neema Tamang</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9824916928</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9824916928</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11673,10 +11695,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.67986</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.67986</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -11732,47 +11752,43 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.33749</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.33749</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>2h 25m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
           <t>Case : router change  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS55" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT55" s="3" t="inlineStr">
-        <is>
-          <t>2h 25m</t>
-        </is>
-      </c>
-      <c r="AU55" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV55" s="3" t="inlineStr">
-        <is>
-          <t>Case : router change  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW55" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -11781,6 +11797,430 @@
       <c r="AX55" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:20 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet is slow   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>internet is slow</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340683</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Sahil Khan</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Sahil Khan</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9803118003</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:04:56 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>CHB9803118003</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:21:25 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:20:58 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>27.70234115431278, 85.30779496606985, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>9803118003@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr"/>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr"/>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>CDB188</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet is slow   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>1h 16m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : internet is slow   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:05 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341494</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Elite Legal Associates PTVLTd</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Elite Legal Associates PTVLTd</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9801146166</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:39:44 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9801146166</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:39:44 PM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:05:49 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.685514</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Kupondol,, Kupondole Rd, ??????? 12646 , Near by Sarvanga Swasthya Sadan Hospital, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>acharyapallav@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr"/>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>CDB233</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.317238</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>26m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>26m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.5%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -865,17 +865,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -893,17 +893,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -1089,7 +1089,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Wire Management request on premises</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1115,31 +1115,59 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Wire Management request on premises</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B13" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="D13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>41</v>
+      <c r="H13" s="4" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX57"/>
+  <dimension ref="A1:AX59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11867,10 +11895,8 @@
           <t>Sahil Khan</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9803118003</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9803118003</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11905,10 +11931,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -11960,25 +11984,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>CDB188</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>Case : internet is slow   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
@@ -12079,10 +12099,8 @@
           <t>Elite Legal Associates PTVLTd</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9801146166</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9801146166</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -12117,10 +12135,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.685514</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.685514</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -12172,47 +12188,43 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>CDB233</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.317238</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.317238</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>26m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>26m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS57" s="3" t="inlineStr">
-        <is>
-          <t>26m</t>
-        </is>
-      </c>
-      <c r="AT57" s="3" t="inlineStr">
-        <is>
-          <t>26m</t>
-        </is>
-      </c>
-      <c r="AU57" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV57" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -12221,6 +12233,418 @@
       <c r="AX57" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:41 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>SLOW ISSUE</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338844</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9842684993</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:41:57 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>BKT9842684993</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:07 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:41:57 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr"/>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur Futsal - Futsal court MC96+P25 Araniko Highway Suryabinayak 44800, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>9842684993@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>13:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr"/>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 19m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX58" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 4:38 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340263</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati bhandari</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:38:23 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9855024115</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 04:38:23 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr"/>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>27. 658629 85.314654, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr"/>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>06:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr"/>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>1d 13m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX59" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -1227,7 +1227,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -12303,10 +12303,8 @@
           <t>Kalpana Baral</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9842684993</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9842684993</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -12396,10 +12394,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
@@ -12410,7 +12406,7 @@
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -12511,10 +12507,8 @@
           <t>Bhagawati bhandari</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9855024115</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9855024115</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -12600,10 +12594,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
@@ -12614,7 +12606,7 @@
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.9%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.5%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX59"/>
+  <dimension ref="A1:AX60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1227,7 +1227,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -12640,6 +12640,214 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 5:05 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340472</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Sabin K.C</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9849450663</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 05:05:13 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9842424578</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 06:19:37 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 05:05:13 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr"/>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>3D Art World - Interactive Museum - Art center M82R+PW2 Mahalaxmi 44700, , ,</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>kcsabin544@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>07:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr"/>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>22h 45m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Sep_2026.xlsx
@@ -1227,7 +1227,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -12707,10 +12707,8 @@
           <t>Sabin K.C</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9849450663</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9849450663</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -12800,10 +12798,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
@@ -12814,7 +12810,7 @@
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
